--- a/output/Data and Chart Outputs/pakistan_gas.xlsx
+++ b/output/Data and Chart Outputs/pakistan_gas.xlsx
@@ -159,6 +159,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Pakistan gas production by province (PBS / DGPC) (to Mar/24)</a:t>
             </a:r>
           </a:p>
@@ -378,7 +379,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pakistan LNG imports by value (PBS) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Pakistan LNG imports by value (PBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -408,12 +410,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - LNG imports'!$A$2:$A$56</f>
+              <f>'Chart - LNG imports'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - LNG imports'!$B$2:$B$56</f>
+              <f>'Chart - LNG imports'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -885,14 +887,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Production monthly 2021-01..2024-03; LNG imports monthly 2022-01..2026-08. PBS has not posted a Monthly Bulletin of Statistics after the September 2024 issue (data to March 2024); the import statements continue monthly (about 18 days after the month).</t>
+          <t>Production monthly 2021-01..2024-03; LNG imports monthly 2022-01..2026-09. PBS has not posted a Monthly Bulletin of Statistics after the September 2024 issue (data to March 2024); the import statements continue monthly (about 18 days after the month).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>79 PBS files read so far (Files sheet).</t>
+          <t>80 PBS files read so far (Files sheet).</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1964,6 +1966,14 @@
       </c>
       <c r="B56" t="n">
         <v>187.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B57" t="n">
+        <v>54.2</v>
       </c>
     </row>
   </sheetData>
@@ -30647,7 +30657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31141,10 +31151,10 @@
         <v>45901</v>
       </c>
       <c r="B46" t="n">
-        <v>207850.7</v>
+        <v>207851</v>
       </c>
       <c r="C46" t="n">
-        <v>58588.5</v>
+        <v>58588</v>
       </c>
     </row>
     <row r="47">
@@ -31262,10 +31272,21 @@
         <v>46235</v>
       </c>
       <c r="B57" t="n">
-        <v>187456.4</v>
+        <v>187456</v>
       </c>
       <c r="C57" t="n">
-        <v>52121.9</v>
+        <v>52122</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="n">
+        <v>54200.7</v>
+      </c>
+      <c r="C58" t="n">
+        <v>15047.7</v>
       </c>
     </row>
   </sheetData>
@@ -31279,7 +31300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32481,6 +32502,21 @@
         </is>
       </c>
       <c r="C80" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.pbs.gov.pk/wp-content/uploads/2020/07/Import_September-2026.xlsx</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Imports</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
         <v>3</v>
       </c>
     </row>
